--- a/human_validation/judge/kor/judge_D010_S004_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D010_S004_P003__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -559,12 +556,124 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 아침에 일어나면 정말 슬프고 텅 빈 느낌이 들어요. 작업실 조명은 켜져 있는데, 제 안에는 더 이상 음악이 없는 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 느낌이 얼마나 오래되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 지금 한 아홉 달 정도 됐어요. 꽤 꾸준히 계속돼 왔어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 인생에서 정반대의 시기, 그러니까 유난히 에너지가 넘치거나 과잉행동을 하거나 잠을 별로 필요로 하지 않는다고 느꼈던 때가 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 눈부시게 살아있다고 느껴지던, 모든 게 다 가능할 것 같던 시기들이 있었어요. 근데 누가 제 계획에 의문을 제기하거나 발목이 아직 쉬어야 한다고 상기시키면 갑자기 화가 확 났어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 그런 에너지가 높은 시기가 있었을 때, 보통 얼마나 지속됐나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 발목 부상 이후에 시작됐고, 이 패턴 전체가 지금 한 두 달 정도 이어지고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 그런 고에너지 시기 동안, 일상적인 책임을 감당하는 데 심각한 어려움을 겪거나 입원이 필요할 정도로 심해진 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 입원까지는 안 했는데, 여러 가지에 지장이 생기긴 했어요. 수업 준비가 밀렸고 지원금 마감을 놓쳤어요. 작업실이 꽤 엉망이 됐고, 협업자들이 기본적인 일정 관리까지 대신 떠맡아야 했어요. 꼭 필요한 것들은 그래도 챙겼는데, 평소 제가 안무가나 교사로서 움직이던 방식으로는 기능하지 못하고 있었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>진단명: 정신병적 양상을 동반한 제1형 양극성장애 (D010)
 인구통계: 성별 여성 / 나이 34 / 직업상태 dancer or choreographer / 최종학력 학사
@@ -573,191 +682,48 @@
 증상 지속 기간: None
 추가 요건: delusions_and_hallucinations occur exclusively during the manic episode
 주호소 증상 코드: S024
-배경 서술: 로렌 댐은 리허설 중 발목에 심각한 부상을 입어 소규모 공연 시리즈를 취소하고, 평소 삶의 틀이 되어주던 등산 기반 안무 작업을 중단할 수밖에 없게 된 뒤 증상이 임상적으로 유의미해졌다. 이후 두 달 동안 움직임을 통한 표현 수단을 잃은 상태에서, 취소된 프로젝트 전체를 다시 설계하려 하고, 협업자들에게 빠른 속도로 말하고, 여러 새로운 예술적 계획을 동시에 추진하며, 산악 풍경을 역사에 남을 작품으로 옮기도록 자신이 선택받았다는 고정되고 과장된 믿음을 갖게 되는, 유난히 에너지가 넘치는 시기가 이어졌고, 이 믿음과 연결된 간헐적이고 생생한 지각 경험도 동반되었다. 이 삽화는 수업과 지원금 마감, 기본적인 작업실 운영에 지장을 주었고, 이어서 우울한 기분, 수면 및 식욕 변화, 정신운동 둔화, 피로감, 무용수들과 지역 파트너들을 실망시켰다는 죄책감이 뒤따랐다. 로렌은 이 패턴이 평범한 창작열이나 부상으로 인한 좌절감의 범위를 넘어선다는 것을 스스로 인식했기에, 1차 진료 의사에게 외래 정신과로의 긴급 의뢰를 요청했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 아침에 일어나면 정말 슬프고 텅 빈 느낌이 들어요. 작업실 조명은 켜져 있는데, 제 안에는 더 이상 음악이 없는 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 느낌이 얼마나 오래되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 지금 한 아홉 달 정도 됐어요. 꽤 꾸준히 계속돼 왔어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 인생에서 정반대의 시기, 그러니까 유난히 에너지가 넘치거나 과잉행동을 하거나 잠을 별로 필요로 하지 않는다고 느꼈던 때가 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 눈부시게 살아있다고 느껴지던, 모든 게 다 가능할 것 같던 시기들이 있었어요. 근데 누가 제 계획에 의문을 제기하거나 발목이 아직 쉬어야 한다고 상기시키면 갑자기 화가 확 났어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 그런 에너지가 높은 시기가 있었을 때, 보통 얼마나 지속됐나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 발목 부상 이후에 시작됐고, 이 패턴 전체가 지금 한 두 달 정도 이어지고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 그런 고에너지 시기 동안, 일상적인 책임을 감당하는 데 심각한 어려움을 겪거나 입원이 필요할 정도로 심해진 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 입원까지는 안 했는데, 여러 가지에 지장이 생기긴 했어요. 수업 준비가 밀렸고 지원금 마감을 놓쳤어요. 작업실이 꽤 엉망이 됐고, 협업자들이 기본적인 일정 관리까지 대신 떠맡아야 했어요. 꼭 필요한 것들은 그래도 챙겼는데, 평소 제가 안무가나 교사로서 움직이던 방식으로는 기능하지 못하고 있었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+배경 서술: 로렌 댐은 리허설 중 발목에 심각한 부상을 입어 소규모 공연 시리즈를 취소하고, 평소 삶의 틀이 되어주던 등산 기반 안무 작업을 중단할 수밖에 없게 된 뒤 증상이 임상적으로 유의미해졌다. 이후 두 달 동안 움직임을 통한 표현 수단을 잃은 상태에서, 취소된 프로젝트 전체를 다시 설계하려 하고, 협업자들에게 빠른 속도로 말하고, 여러 새로운 예술적 계획을 동시에 추진하며, 산악 풍경을 역사에 남을 작품으로 옮기도록 자신이 선택받았다는 고정되고 과장된 믿음을 갖게 되는, 유난히 에너지가 넘치는 시기가 이어졌고, 이 믿음과 연결된 간헐적이고 생생한 지각 경험도 동반되었다. 이 삽화는 수업과 지원금 마감, 기본적인 작업실 운영에 지장을 주었고, 이어서 우울한 기분, 수면 및 식욕 변화, 정신운동 둔화, 피로감, 무용수들과 지역 파트너들을 실망시켰다는 죄책감이 뒤따랐다. 로렌은 이 패턴이 평범한 창작열이나 부상으로 인한 좌절감의 범위를 넘어선다는 것을 스스로 인식했기에, 1차 진료 의사에게 외래 정신과로의 긴급 의뢰를 요청했다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S035 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
+  - S037 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.
+  - S039 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.
+  - S040 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.</t>
+        </is>
+      </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: None (None, ICD: F31)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=1, 커버리지=0.2)
-  확인된 근거: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
-  누락: 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.; 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).; 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=1, 커버리지=0.2)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
-  누락: 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
+          <t>의사의 최종 진단: None (None, ICD: F31)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=1, 커버리지=0.2)
+확인된 근거:
+  - 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=1, 커버리지=0.2)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D010_S004_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D010_S004_P003__gemini-3.8-flash_kor.xlsx
@@ -668,6 +668,11 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -719,11 +724,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D010_S004_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D010_S004_P003__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.0667</v>
+        <v>0.0857</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.075</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -553,6 +554,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
